--- a/data/Playoffs.xlsx
+++ b/data/Playoffs.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="169">
   <si>
     <t>Année</t>
   </si>
@@ -130,6 +130,9 @@
     <t>Lakers - Suns</t>
   </si>
   <si>
+    <t>https://youtu.be/AVbOYBb-rxM?si=KIGRPcuOi9UklRC4</t>
+  </si>
+  <si>
     <t>https://youtu.be/yIysF9LT3ss?si=-z7S15zT_8y0J02t</t>
   </si>
   <si>
@@ -142,6 +145,9 @@
     <t>https://youtu.be/MhDuHQp1ClQ?si=lW-3gEaN7GNtz_IN</t>
   </si>
   <si>
+    <t>https://youtu.be/uDvCZhj_Zgc?si=1bUWpLu3ZdS97-6d</t>
+  </si>
+  <si>
     <t>https://youtu.be/vLTNfZeDMI4?si=X1LsQcVzGTBXRQqk</t>
   </si>
   <si>
@@ -295,12 +301,21 @@
     <t>https://youtu.be/sU3qXCws9As?si=IKXmrZSLjJDQRbIP</t>
   </si>
   <si>
+    <t>https://youtu.be/Vj5V039ddqI?si=u8dEA-iSl0uhZ1xz</t>
+  </si>
+  <si>
+    <t>https://youtu.be/PWzdAga5CAk?si=_wxQsP7V6v6b5Z_O</t>
+  </si>
+  <si>
     <t>Suns - Nuggets</t>
   </si>
   <si>
     <t>Sonics - Rockets</t>
   </si>
   <si>
+    <t>https://youtu.be/e5XN6C5I4OE?si=VWeyekLohHLHIrqQ</t>
+  </si>
+  <si>
     <t>Spurs - Pistons</t>
   </si>
   <si>
@@ -424,6 +439,9 @@
     <t>Pistons - Sixers</t>
   </si>
   <si>
+    <t>https://youtu.be/tQVEzEZfMV4?si=v2wR3NqmR9IOaXYT</t>
+  </si>
+  <si>
     <t>https://youtu.be/bFGtupkU_qE?si=1I3ZGqaAuscXtATL</t>
   </si>
   <si>
@@ -431,6 +449,9 @@
   </si>
   <si>
     <t>Pacers - Celtics</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WAWjH7M9nDo?si=L5K2Np2hRYrqPp-f</t>
   </si>
   <si>
     <t>Heat - Nets</t>
@@ -520,7 +541,7 @@
       <color rgb="FF0000FF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -539,6 +560,12 @@
         <bgColor theme="5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -546,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -560,6 +587,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -955,14 +985,14 @@
       <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
+      <c r="D7" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>28</v>
@@ -979,28 +1009,28 @@
         <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>28</v>
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1008,10 +1038,10 @@
         <v>1980.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>28</v>
@@ -1028,10 +1058,10 @@
         <v>1980.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>28</v>
@@ -1045,10 +1075,10 @@
         <v>1980.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>28</v>
@@ -1065,16 +1095,16 @@
         <v>1980.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>28</v>
@@ -1088,19 +1118,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -1111,25 +1141,25 @@
         <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1152,7 +1182,7 @@
         <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -1163,25 +1193,25 @@
         <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -1192,7 +1222,7 @@
         <v>32</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>28</v>
@@ -1204,7 +1234,7 @@
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -1227,7 +1257,7 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -1238,7 +1268,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>28</v>
@@ -1261,25 +1291,25 @@
         <v>1989.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
@@ -1287,10 +1317,10 @@
         <v>1989.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>28</v>
@@ -1307,10 +1337,10 @@
         <v>1989.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>28</v>
@@ -1319,7 +1349,7 @@
         <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>28</v>
@@ -1332,20 +1362,20 @@
       <c r="A23" s="1">
         <v>1989.0</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>46</v>
+      <c r="B23" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1353,10 +1383,10 @@
         <v>1989.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>28</v>
@@ -1372,20 +1402,20 @@
       <c r="A25" s="1">
         <v>1989.0</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>49</v>
+      <c r="B25" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>28</v>
+        <v>95</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="26">
@@ -1393,10 +1423,10 @@
         <v>1989.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>28</v>
@@ -1413,10 +1443,10 @@
         <v>1989.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>28</v>
@@ -1427,8 +1457,8 @@
       <c r="F27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>28</v>
+      <c r="G27" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1439,28 +1469,28 @@
         <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29">
@@ -1471,28 +1501,28 @@
         <v>18</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30">
@@ -1503,22 +1533,22 @@
         <v>25</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31">
@@ -1529,7 +1559,7 @@
         <v>32</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>28</v>
@@ -1538,7 +1568,7 @@
         <v>28</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>28</v>
@@ -1547,7 +1577,7 @@
         <v>28</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32">
@@ -1558,13 +1588,13 @@
         <v>32</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>28</v>
@@ -1581,25 +1611,25 @@
         <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
@@ -1610,25 +1640,25 @@
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35">
@@ -1636,25 +1666,25 @@
         <v>2005.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>28</v>
+        <v>141</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36">
@@ -1662,16 +1692,16 @@
         <v>2005.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>28</v>
+      <c r="E36" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>28</v>
@@ -1694,10 +1724,10 @@
         <v>2005.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>28</v>
@@ -1706,7 +1736,7 @@
         <v>28</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>28</v>
@@ -1717,10 +1747,10 @@
         <v>2005.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>28</v>
@@ -1735,10 +1765,10 @@
         <v>28</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39">
@@ -1746,16 +1776,16 @@
         <v>2005.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>28</v>
@@ -1764,10 +1794,10 @@
         <v>28</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>28</v>
@@ -1778,22 +1808,22 @@
         <v>2005.0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41">
@@ -1801,10 +1831,10 @@
         <v>2005.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>28</v>
@@ -1827,25 +1857,25 @@
         <v>2005.0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -1867,95 +1897,102 @@
     <hyperlink r:id="rId15" ref="H4"/>
     <hyperlink r:id="rId16" ref="D6"/>
     <hyperlink r:id="rId17" ref="H6"/>
-    <hyperlink r:id="rId18" ref="F7"/>
-    <hyperlink r:id="rId19" ref="D8"/>
-    <hyperlink r:id="rId20" ref="E8"/>
-    <hyperlink r:id="rId21" ref="G8"/>
-    <hyperlink r:id="rId22" ref="I8"/>
-    <hyperlink r:id="rId23" ref="J8"/>
-    <hyperlink r:id="rId24" ref="D12"/>
-    <hyperlink r:id="rId25" ref="E12"/>
-    <hyperlink r:id="rId26" ref="D13"/>
-    <hyperlink r:id="rId27" ref="E13"/>
-    <hyperlink r:id="rId28" ref="F13"/>
-    <hyperlink r:id="rId29" ref="G13"/>
-    <hyperlink r:id="rId30" ref="D14"/>
-    <hyperlink r:id="rId31" ref="E14"/>
-    <hyperlink r:id="rId32" ref="F14"/>
-    <hyperlink r:id="rId33" ref="G14"/>
-    <hyperlink r:id="rId34" ref="H14"/>
-    <hyperlink r:id="rId35" ref="I14"/>
-    <hyperlink r:id="rId36" ref="G15"/>
-    <hyperlink r:id="rId37" ref="D16"/>
-    <hyperlink r:id="rId38" ref="E16"/>
-    <hyperlink r:id="rId39" ref="F16"/>
-    <hyperlink r:id="rId40" ref="G16"/>
-    <hyperlink r:id="rId41" ref="H16"/>
-    <hyperlink r:id="rId42" ref="I16"/>
-    <hyperlink r:id="rId43" ref="G17"/>
-    <hyperlink r:id="rId44" ref="G18"/>
-    <hyperlink r:id="rId45" ref="D20"/>
-    <hyperlink r:id="rId46" ref="E20"/>
-    <hyperlink r:id="rId47" ref="F20"/>
-    <hyperlink r:id="rId48" ref="G20"/>
-    <hyperlink r:id="rId49" ref="H20"/>
-    <hyperlink r:id="rId50" ref="F22"/>
-    <hyperlink r:id="rId51" ref="D23"/>
-    <hyperlink r:id="rId52" ref="E23"/>
-    <hyperlink r:id="rId53" ref="F23"/>
-    <hyperlink r:id="rId54" ref="D25"/>
-    <hyperlink r:id="rId55" ref="D28"/>
-    <hyperlink r:id="rId56" ref="E28"/>
-    <hyperlink r:id="rId57" ref="F28"/>
-    <hyperlink r:id="rId58" ref="G28"/>
-    <hyperlink r:id="rId59" ref="H28"/>
-    <hyperlink r:id="rId60" ref="I28"/>
-    <hyperlink r:id="rId61" ref="J28"/>
-    <hyperlink r:id="rId62" ref="D29"/>
-    <hyperlink r:id="rId63" ref="E29"/>
-    <hyperlink r:id="rId64" ref="G29"/>
-    <hyperlink r:id="rId65" ref="H29"/>
-    <hyperlink r:id="rId66" ref="I29"/>
-    <hyperlink r:id="rId67" ref="J29"/>
-    <hyperlink r:id="rId68" ref="D30"/>
-    <hyperlink r:id="rId69" ref="E30"/>
-    <hyperlink r:id="rId70" ref="F30"/>
-    <hyperlink r:id="rId71" ref="G30"/>
-    <hyperlink r:id="rId72" ref="H30"/>
-    <hyperlink r:id="rId73" ref="F31"/>
-    <hyperlink r:id="rId74" ref="I31"/>
-    <hyperlink r:id="rId75" ref="D32"/>
-    <hyperlink r:id="rId76" ref="E32"/>
-    <hyperlink r:id="rId77" ref="D33"/>
-    <hyperlink r:id="rId78" ref="F33"/>
-    <hyperlink r:id="rId79" ref="G33"/>
-    <hyperlink r:id="rId80" ref="H33"/>
-    <hyperlink r:id="rId81" ref="I33"/>
-    <hyperlink r:id="rId82" ref="D34"/>
-    <hyperlink r:id="rId83" ref="E34"/>
-    <hyperlink r:id="rId84" ref="F34"/>
-    <hyperlink r:id="rId85" ref="G34"/>
-    <hyperlink r:id="rId86" ref="H34"/>
-    <hyperlink r:id="rId87" ref="I34"/>
-    <hyperlink r:id="rId88" ref="F35"/>
-    <hyperlink r:id="rId89" ref="H35"/>
-    <hyperlink r:id="rId90" ref="F37"/>
-    <hyperlink r:id="rId91" ref="H38"/>
-    <hyperlink r:id="rId92" ref="I38"/>
-    <hyperlink r:id="rId93" ref="D39"/>
-    <hyperlink r:id="rId94" ref="E39"/>
-    <hyperlink r:id="rId95" ref="H39"/>
-    <hyperlink r:id="rId96" ref="I39"/>
-    <hyperlink r:id="rId97" ref="D40"/>
-    <hyperlink r:id="rId98" ref="E40"/>
-    <hyperlink r:id="rId99" ref="F40"/>
-    <hyperlink r:id="rId100" ref="G40"/>
-    <hyperlink r:id="rId101" ref="D42"/>
-    <hyperlink r:id="rId102" ref="E42"/>
-    <hyperlink r:id="rId103" ref="F42"/>
-    <hyperlink r:id="rId104" ref="G42"/>
-    <hyperlink r:id="rId105" ref="H42"/>
+    <hyperlink r:id="rId18" ref="D7"/>
+    <hyperlink r:id="rId19" ref="F7"/>
+    <hyperlink r:id="rId20" ref="D8"/>
+    <hyperlink r:id="rId21" ref="E8"/>
+    <hyperlink r:id="rId22" ref="F8"/>
+    <hyperlink r:id="rId23" ref="G8"/>
+    <hyperlink r:id="rId24" ref="I8"/>
+    <hyperlink r:id="rId25" ref="J8"/>
+    <hyperlink r:id="rId26" ref="D12"/>
+    <hyperlink r:id="rId27" ref="E12"/>
+    <hyperlink r:id="rId28" ref="D13"/>
+    <hyperlink r:id="rId29" ref="E13"/>
+    <hyperlink r:id="rId30" ref="F13"/>
+    <hyperlink r:id="rId31" ref="G13"/>
+    <hyperlink r:id="rId32" ref="D14"/>
+    <hyperlink r:id="rId33" ref="E14"/>
+    <hyperlink r:id="rId34" ref="F14"/>
+    <hyperlink r:id="rId35" ref="G14"/>
+    <hyperlink r:id="rId36" ref="H14"/>
+    <hyperlink r:id="rId37" ref="I14"/>
+    <hyperlink r:id="rId38" ref="G15"/>
+    <hyperlink r:id="rId39" ref="D16"/>
+    <hyperlink r:id="rId40" ref="E16"/>
+    <hyperlink r:id="rId41" ref="F16"/>
+    <hyperlink r:id="rId42" ref="G16"/>
+    <hyperlink r:id="rId43" ref="H16"/>
+    <hyperlink r:id="rId44" ref="I16"/>
+    <hyperlink r:id="rId45" ref="G17"/>
+    <hyperlink r:id="rId46" ref="G18"/>
+    <hyperlink r:id="rId47" ref="D20"/>
+    <hyperlink r:id="rId48" ref="E20"/>
+    <hyperlink r:id="rId49" ref="F20"/>
+    <hyperlink r:id="rId50" ref="G20"/>
+    <hyperlink r:id="rId51" ref="H20"/>
+    <hyperlink r:id="rId52" ref="F22"/>
+    <hyperlink r:id="rId53" ref="D23"/>
+    <hyperlink r:id="rId54" ref="E23"/>
+    <hyperlink r:id="rId55" ref="F23"/>
+    <hyperlink r:id="rId56" ref="D25"/>
+    <hyperlink r:id="rId57" ref="E25"/>
+    <hyperlink r:id="rId58" ref="F25"/>
+    <hyperlink r:id="rId59" ref="G27"/>
+    <hyperlink r:id="rId60" ref="D28"/>
+    <hyperlink r:id="rId61" ref="E28"/>
+    <hyperlink r:id="rId62" ref="F28"/>
+    <hyperlink r:id="rId63" ref="G28"/>
+    <hyperlink r:id="rId64" ref="H28"/>
+    <hyperlink r:id="rId65" ref="I28"/>
+    <hyperlink r:id="rId66" ref="J28"/>
+    <hyperlink r:id="rId67" ref="D29"/>
+    <hyperlink r:id="rId68" ref="E29"/>
+    <hyperlink r:id="rId69" ref="G29"/>
+    <hyperlink r:id="rId70" ref="H29"/>
+    <hyperlink r:id="rId71" ref="I29"/>
+    <hyperlink r:id="rId72" ref="J29"/>
+    <hyperlink r:id="rId73" ref="D30"/>
+    <hyperlink r:id="rId74" ref="E30"/>
+    <hyperlink r:id="rId75" ref="F30"/>
+    <hyperlink r:id="rId76" ref="G30"/>
+    <hyperlink r:id="rId77" ref="H30"/>
+    <hyperlink r:id="rId78" ref="F31"/>
+    <hyperlink r:id="rId79" ref="I31"/>
+    <hyperlink r:id="rId80" ref="D32"/>
+    <hyperlink r:id="rId81" ref="E32"/>
+    <hyperlink r:id="rId82" ref="D33"/>
+    <hyperlink r:id="rId83" ref="F33"/>
+    <hyperlink r:id="rId84" ref="G33"/>
+    <hyperlink r:id="rId85" ref="H33"/>
+    <hyperlink r:id="rId86" ref="I33"/>
+    <hyperlink r:id="rId87" ref="D34"/>
+    <hyperlink r:id="rId88" ref="E34"/>
+    <hyperlink r:id="rId89" ref="F34"/>
+    <hyperlink r:id="rId90" ref="G34"/>
+    <hyperlink r:id="rId91" ref="H34"/>
+    <hyperlink r:id="rId92" ref="I34"/>
+    <hyperlink r:id="rId93" ref="D35"/>
+    <hyperlink r:id="rId94" ref="F35"/>
+    <hyperlink r:id="rId95" ref="H35"/>
+    <hyperlink r:id="rId96" ref="E36"/>
+    <hyperlink r:id="rId97" ref="F37"/>
+    <hyperlink r:id="rId98" ref="H38"/>
+    <hyperlink r:id="rId99" ref="I38"/>
+    <hyperlink r:id="rId100" ref="D39"/>
+    <hyperlink r:id="rId101" ref="E39"/>
+    <hyperlink r:id="rId102" ref="H39"/>
+    <hyperlink r:id="rId103" ref="I39"/>
+    <hyperlink r:id="rId104" ref="D40"/>
+    <hyperlink r:id="rId105" ref="E40"/>
+    <hyperlink r:id="rId106" ref="F40"/>
+    <hyperlink r:id="rId107" ref="G40"/>
+    <hyperlink r:id="rId108" ref="D42"/>
+    <hyperlink r:id="rId109" ref="E42"/>
+    <hyperlink r:id="rId110" ref="F42"/>
+    <hyperlink r:id="rId111" ref="G42"/>
+    <hyperlink r:id="rId112" ref="H42"/>
   </hyperlinks>
-  <drawing r:id="rId106"/>
+  <drawing r:id="rId113"/>
 </worksheet>
 </file>